--- a/web/public/forms/gy-jikbul.xlsx
+++ b/web/public/forms/gy-jikbul.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접지급합의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접지급 합의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'직접지급합의서'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'직접지급 합의서'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="&quot;₩&quot;#,##0;[Red]-&quot;₩&quot;#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="[DBNum4][$-412]&quot;일금 &quot;General&quot;원정&quot;;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy. m. d."/>
+    <numFmt numFmtId="167" formatCode="&quot;~ &quot;yyyy. m. d."/>
+    <numFmt numFmtId="168" formatCode="&quot;(총 &quot;#,##0&quot;일)&quot;;;&quot;&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,32 +40,99 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="16"/>
-      <u val="single"/>
+      <color rgb="000F203F"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="006B7280"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="12"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,126 +142,88 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,352 +589,933 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>하도급대금 직접지급 합의서(표준 양식)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>하도급대금 직접지급 합의서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>원 도 급
 계약사항</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>공 사 명</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>도급 계약금액</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="8">
+        <f>IF(N(D6)=0,"",D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>계약기간</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11">
+        <f>IF(OR(N(D7)=0,N(E7)=0),"",E7-D7+1)</f>
+        <v/>
+      </c>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>하 도 급
 계약사항</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>공사명(공종명)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>계약 내용</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>공사명
+(공종명)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>하도급계약금액</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="8">
+        <f>IF(N(D9)=0,"",D9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>계약기간</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="11">
+        <f>IF(OR(N(D10)=0,N(E10)=0),"",E10-D10+1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>발 주 자</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>상 호 및
+대 표 자</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>수 급 인</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>상 호 및 대표자</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>주 소</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>상 호 및 대표자</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>주 소</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>상 호 및
+대 표 자</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>하수급인</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>상 호 및 대표자</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>주 소</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>1. 상기 수급인과 하수급인간의 하도급계약에 있어 하수급이 시공한 분에 해당하는 하도급대금을 건설산업기본법 제35조제2항의 규정에 따라 발주자가 하수급인에게 직접지급하기로 발주자·수급인 및 하수급인간에 합의합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>상 호 및
+대 표 자</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="12">
+        <f>IF(AND(N(D9)&gt;0,N(D6)&gt;0,D9&gt;D6),"⚠ 하도급 계약금액이 도급 계약금액보다 큽니다. ","")&amp;IF(AND(N(D10)&gt;0,N(D7)&gt;0,N(E10)&gt;0,N(E7)&gt;0),IF(OR(D10&lt;D7,E10&gt;E7),"⚠ 하도급 계약기간이 원도급 계약기간을 벗어납니다.",""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="4" customHeight="1"/>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>1. 상기 수급인과 하수급인간의 하도급계약에 있어 하수급인이 시공한 부분에 해당하는 하도급대금을 건설산업기본법 제35조제2항의 규정에 따라 발주자가 하수급인에게 직접지급하기로 발주자·수급인 및 하수급인간에 합의합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>2. 하도급대금 직접지급 방법 및 절차</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 수급인은 기성검사 및 준공검사시 하수급인이 시공한 부분에 대한 내역을 구분하여 신청하고 하도급대금의 지급청구도 분리하여 청구하여야 하며, 발주자는 하도급대금을 하수급인에게 아래 계좌로 직접지급 하기로 합니다.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>◈ 하수급인 예금계좌</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>예금주</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>은행명</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>계좌번호(하도급지킴이 고정계좌)</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-    </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>예 금 주</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>은 행 명</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>계좌번호 (하도급지킴이 고정계좌)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="10" customHeight="1"/>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>3. 건설산업기본법 제35조제5항의 규정에 따라 발주자는 수급인이 하도급계약과 관련하여 하수급인이 임금, 자재대금 등의 지급을 지체한 사실을 입증할 수 있는 서류를 첨부하여 그 하도급대금의 직접지급의 중지를 요청한 경우에는 하수급인에게 하도급대금을 직접 지급하지 아니할 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>년          월          일</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="B28" s="8" t="inlineStr">
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="17" t="inlineStr"/>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년          월          일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="17" t="inlineStr"/>
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>발 주 자 :</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="C32" s="20">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>(인)</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="17" t="inlineStr"/>
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>수 급 인 :</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="C33" s="20">
+        <f>IF(D13="","",D13)</f>
+        <v/>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>(인)</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="B30" s="8" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="17" t="inlineStr"/>
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>하수급인 :</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="C34" s="20">
+        <f>IF(D15="","",D15)</f>
+        <v/>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>(인)</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>하늘색 칸 = 자동(금액 한글 표기 · 계약 일수). 날인란 이름은 위 «상호 및 대표자» 칸을 그대로 따라옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>하도급 금액이 원도급보다 크거나, 하도급 기간이 원도급 기간을 벗어나면 표 아래에 빨간 경고가 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>계좌는 하도급지킴이 고정계좌를 적습니다. 발주기관이 정한 서식이 있으면 그 서식을 쓰세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="E1" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>하도급대금 직접지급 합의서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>원 도 급
+계약사항</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>공 사 명</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>도급 계약금액</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="8">
+        <f>IF(N(D6)=0,"",D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>계약기간</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>46387</v>
+      </c>
+      <c r="F7" s="11">
+        <f>IF(OR(N(D7)=0,N(E7)=0),"",E7-D7+1)</f>
+        <v/>
+      </c>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>하 도 급
+계약사항</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>계약 내용</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>공사명
+(공종명)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사 중 구조물공(암거)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>하도급계약금액</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>285000000</v>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="8">
+        <f>IF(N(D9)=0,"",D9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>계약기간</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F10" s="11">
+        <f>IF(OR(N(D10)=0,N(E10)=0),"",E10-D10+1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>발 주 자</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>상 호 및
+대 표 자</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>가나시장</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>가나시 가나로 1</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>수 급 인</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>상 호 및
+대 표 자</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>예시건설(주) 대표이사 홍길동</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>하수급인</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>상 호 및
+대 표 자</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>(주)예시토건 대표이사 나대표</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>가나시 가나로 12</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="12">
+        <f>IF(AND(N(D9)&gt;0,N(D6)&gt;0,D9&gt;D6),"⚠ 하도급 계약금액이 도급 계약금액보다 큽니다. ","")&amp;IF(AND(N(D10)&gt;0,N(D7)&gt;0,N(E10)&gt;0,N(E7)&gt;0),IF(OR(D10&lt;D7,E10&gt;E7),"⚠ 하도급 계약기간이 원도급 계약기간을 벗어납니다.",""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="4" customHeight="1"/>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>1. 상기 수급인과 하수급인간의 하도급계약에 있어 하수급인이 시공한 부분에 해당하는 하도급대금을 건설산업기본법 제35조제2항의 규정에 따라 발주자가 하수급인에게 직접지급하기로 발주자·수급인 및 하수급인간에 합의합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>2. 하도급대금 직접지급 방법 및 절차</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 수급인은 기성검사 및 준공검사시 하수급인이 시공한 부분에 대한 내역을 구분하여 신청하고 하도급대금의 지급청구도 분리하여 청구하여야 하며, 발주자는 하도급대금을 하수급인에게 아래 계좌로 직접지급 하기로 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>◈ 하수급인 예금계좌</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>예 금 주</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>은 행 명</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>계좌번호 (하도급지킴이 고정계좌)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>(주)예시토건</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>예시은행</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>000-000000-00-000</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="10" customHeight="1"/>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>3. 건설산업기본법 제35조제5항의 규정에 따라 발주자는 수급인이 하도급계약과 관련하여 하수급인이 임금, 자재대금 등의 지급을 지체한 사실을 입증할 수 있는 서류를 첨부하여 그 하도급대금의 직접지급의 중지를 요청한 경우에는 하수급인에게 하도급대금을 직접 지급하지 아니할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="17" t="inlineStr"/>
+      <c r="D30" s="18" t="n">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="17" t="inlineStr"/>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>발 주 자 :</t>
+        </is>
+      </c>
+      <c r="C32" s="20">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>(인)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="17" t="inlineStr"/>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>수 급 인 :</t>
+        </is>
+      </c>
+      <c r="C33" s="20">
+        <f>IF(D13="","",D13)</f>
+        <v/>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>(인)</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="17" t="inlineStr"/>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>하수급인 :</t>
+        </is>
+      </c>
+      <c r="C34" s="20">
+        <f>IF(D15="","",D15)</f>
+        <v/>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>(인)</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 계좌). 실제로는 앞 시트에 적으세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="C8"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D9:G9"/>
     <mergeCell ref="A17:G17"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="D8:G8"/>
-    <mergeCell ref="C7"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D15:G15"/>
     <mergeCell ref="D5:G5"/>
-    <mergeCell ref="C13"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="C3"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="C6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="C14"/>
-    <mergeCell ref="C5"/>
-    <mergeCell ref="A3:B5"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C4"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="C10"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B8:B10"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D13:G13"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C9"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="C12"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C11"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/gy-jikbul.xlsx
+++ b/web/public/forms/gy-jikbul.xlsx
@@ -604,7 +604,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="22" t="inlineStr">

--- a/web/public/forms/gy-jikbul.xlsx
+++ b/web/public/forms/gy-jikbul.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접지급 합의서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'직접지급 합의서'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -158,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -220,9 +218,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -650,10 +645,7 @@
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="8">
-        <f>IF(N(D6)=0,"",D6)</f>
-        <v/>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="5" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -666,10 +658,7 @@
       </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="10" t="n"/>
-      <c r="F7" s="11">
-        <f>IF(OR(N(D7)=0,N(E7)=0),"",E7-D7+1)</f>
-        <v/>
-      </c>
+      <c r="F7" s="11" t="n"/>
       <c r="G7" s="5" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -705,10 +694,7 @@
       </c>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="8">
-        <f>IF(N(D9)=0,"",D9)</f>
-        <v/>
-      </c>
+      <c r="F9" s="8" t="n"/>
       <c r="G9" s="5" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -721,10 +707,7 @@
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="10" t="n"/>
-      <c r="F10" s="11">
-        <f>IF(OR(N(D10)=0,N(E10)=0),"",E10-D10+1)</f>
-        <v/>
-      </c>
+      <c r="F10" s="11" t="n"/>
       <c r="G10" s="5" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
@@ -821,10 +804,7 @@
       <c r="G16" s="5" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12">
-        <f>IF(AND(N(D9)&gt;0,N(D6)&gt;0,D9&gt;D6),"⚠ 하도급 계약금액이 도급 계약금액보다 큽니다. ","")&amp;IF(AND(N(D10)&gt;0,N(D7)&gt;0,N(E10)&gt;0,N(E7)&gt;0),IF(OR(D10&lt;D7,E10&gt;E7),"⚠ 하도급 계약기간이 원도급 계약기간을 벗어납니다.",""),"")</f>
-        <v/>
-      </c>
+      <c r="A17" s="12" t="n"/>
     </row>
     <row r="18" ht="4" customHeight="1"/>
     <row r="19" ht="48" customHeight="1">
@@ -912,10 +892,7 @@
           <t>발 주 자 :</t>
         </is>
       </c>
-      <c r="C32" s="20">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
+      <c r="C32" s="20" t="n"/>
       <c r="F32" s="20" t="inlineStr">
         <is>
           <t>(인)</t>
@@ -930,10 +907,7 @@
           <t>수 급 인 :</t>
         </is>
       </c>
-      <c r="C33" s="20">
-        <f>IF(D13="","",D13)</f>
-        <v/>
-      </c>
+      <c r="C33" s="20" t="n"/>
       <c r="F33" s="20" t="inlineStr">
         <is>
           <t>(인)</t>
@@ -948,10 +922,7 @@
           <t>하수급인 :</t>
         </is>
       </c>
-      <c r="C34" s="20">
-        <f>IF(D15="","",D15)</f>
-        <v/>
-      </c>
+      <c r="C34" s="20" t="n"/>
       <c r="F34" s="20" t="inlineStr">
         <is>
           <t>(인)</t>
@@ -959,6 +930,7 @@
       </c>
       <c r="G34" s="17" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="21" t="inlineStr">
         <is>
@@ -1030,492 +1002,4 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="E1" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>하도급대금 직접지급 합의서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="8" customHeight="1"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>원 도 급
-계약사항</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>도급 계약금액</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="8">
-        <f>IF(N(D6)=0,"",D6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>계약기간</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F7" s="11">
-        <f>IF(OR(N(D7)=0,N(E7)=0),"",E7-D7+1)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>하 도 급
-계약사항</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>계약 내용</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>공사명
-(공종명)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사 중 구조물공(암거)</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>하도급계약금액</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="8">
-        <f>IF(N(D9)=0,"",D9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>계약기간</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>46326</v>
-      </c>
-      <c r="F10" s="11">
-        <f>IF(OR(N(D10)=0,N(E10)=0),"",E10-D10+1)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>발 주 자</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>상 호 및
-대 표 자</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>가나시장</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>가나시 가나로 1</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>수 급 인</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>상 호 및
-대 표 자</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>예시건설(주) 대표이사 홍길동</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>하수급인</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>상 호 및
-대 표 자</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>(주)예시토건 대표이사 나대표</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>가나시 가나로 12</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12">
-        <f>IF(AND(N(D9)&gt;0,N(D6)&gt;0,D9&gt;D6),"⚠ 하도급 계약금액이 도급 계약금액보다 큽니다. ","")&amp;IF(AND(N(D10)&gt;0,N(D7)&gt;0,N(E10)&gt;0,N(E7)&gt;0),IF(OR(D10&lt;D7,E10&gt;E7),"⚠ 하도급 계약기간이 원도급 계약기간을 벗어납니다.",""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="4" customHeight="1"/>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>1. 상기 수급인과 하수급인간의 하도급계약에 있어 하수급인이 시공한 부분에 해당하는 하도급대금을 건설산업기본법 제35조제2항의 규정에 따라 발주자가 하수급인에게 직접지급하기로 발주자·수급인 및 하수급인간에 합의합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>2. 하도급대금 직접지급 방법 및 절차</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 수급인은 기성검사 및 준공검사시 하수급인이 시공한 부분에 대한 내역을 구분하여 신청하고 하도급대금의 지급청구도 분리하여 청구하여야 하며, 발주자는 하도급대금을 하수급인에게 아래 계좌로 직접지급 하기로 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>◈ 하수급인 예금계좌</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>예 금 주</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>은 행 명</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>계좌번호 (하도급지킴이 고정계좌)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>(주)예시토건</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>예시은행</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>000-000000-00-000</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="10" customHeight="1"/>
-    <row r="28" ht="64" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>3. 건설산업기본법 제35조제5항의 규정에 따라 발주자는 수급인이 하도급계약과 관련하여 하수급인이 임금, 자재대금 등의 지급을 지체한 사실을 입증할 수 있는 서류를 첨부하여 그 하도급대금의 직접지급의 중지를 요청한 경우에는 하수급인에게 하도급대금을 직접 지급하지 아니할 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="D30" s="18" t="n">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>발 주 자 :</t>
-        </is>
-      </c>
-      <c r="C32" s="20">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr"/>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="17" t="inlineStr"/>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>수 급 인 :</t>
-        </is>
-      </c>
-      <c r="C33" s="20">
-        <f>IF(D13="","",D13)</f>
-        <v/>
-      </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="17" t="inlineStr"/>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>하수급인 :</t>
-        </is>
-      </c>
-      <c r="C34" s="20">
-        <f>IF(D15="","",D15)</f>
-        <v/>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 계좌). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A8:A16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A5:B7"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="E1:G1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/gy-jikbul.xlsx
+++ b/web/public/forms/gy-jikbul.xlsx
@@ -599,7 +599,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
